--- a/product_selector_out/STM32F0x2.xlsx
+++ b/product_selector_out/STM32F0x2.xlsx
@@ -42,7 +42,7 @@
       <sz val="11"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -74,6 +74,11 @@
         <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9EAD3"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -90,7 +95,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="11">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="bottom"/>
@@ -105,6 +110,7 @@
     <xf numFmtId="0" fontId="2" fillId="4" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="6" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="2" fillId="7" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -6574,14 +6580,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S12" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R12" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S12" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T12" s="6" t="inlineStr">
@@ -6669,14 +6675,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK12" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL12" s="8" t="inlineStr">
+      <c r="AK12" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL12" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM12" s="9" t="inlineStr">
@@ -7555,14 +7561,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S15" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S15" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T15" s="6" t="inlineStr">
@@ -7650,14 +7656,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK15" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL15" s="8" t="inlineStr">
+      <c r="AK15" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL15" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM15" s="9" t="inlineStr">
@@ -7882,14 +7888,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R16" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S16" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R16" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S16" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T16" s="6" t="inlineStr">
@@ -7977,14 +7983,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK16" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL16" s="8" t="inlineStr">
+      <c r="AK16" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL16" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM16" s="9" t="inlineStr">
@@ -8209,14 +8215,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S17" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S17" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T17" s="6" t="inlineStr">
@@ -8304,14 +8310,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK17" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL17" s="8" t="inlineStr">
+      <c r="AK17" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL17" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM17" s="9" t="inlineStr">
@@ -9190,14 +9196,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S20" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S20" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T20" s="6" t="inlineStr">
@@ -9285,14 +9291,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK20" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL20" s="8" t="inlineStr">
+      <c r="AK20" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL20" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM20" s="9" t="inlineStr">
@@ -9844,14 +9850,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R22" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S22" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S22" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T22" s="6" t="inlineStr">
@@ -9939,14 +9945,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK22" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL22" s="8" t="inlineStr">
+      <c r="AK22" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL22" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM22" s="9" t="inlineStr">
@@ -10498,14 +10504,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S24" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S24" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T24" s="6" t="inlineStr">
@@ -10588,19 +10594,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK24" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL24" s="8" t="inlineStr">
+      <c r="AJ24" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK24" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL24" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM24" s="9" t="inlineStr">
@@ -10825,14 +10831,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S25" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S25" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T25" s="6" t="inlineStr">
@@ -10915,19 +10921,19 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="AJ25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AK25" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL25" s="8" t="inlineStr">
+      <c r="AJ25" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AK25" s="8" t="inlineStr">
+        <is>
+          <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL25" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM25" s="9" t="inlineStr">
@@ -11152,14 +11158,14 @@
           <t>UNAVAILABLE</t>
         </is>
       </c>
-      <c r="R26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="S26" s="7" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
+      <c r="R26" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
+        </is>
+      </c>
+      <c r="S26" s="10" t="inlineStr">
+        <is>
+          <t>DERIVED</t>
         </is>
       </c>
       <c r="T26" s="6" t="inlineStr">
@@ -11247,14 +11253,14 @@
           <t>DATASHEET</t>
         </is>
       </c>
-      <c r="AK26" s="6" t="inlineStr">
-        <is>
-          <t>API</t>
-        </is>
-      </c>
-      <c r="AL26" s="8" t="inlineStr">
+      <c r="AK26" s="8" t="inlineStr">
         <is>
           <t>DATASHEET</t>
+        </is>
+      </c>
+      <c r="AL26" s="6" t="inlineStr">
+        <is>
+          <t>API</t>
         </is>
       </c>
       <c r="AM26" s="9" t="inlineStr">
@@ -11408,7 +11414,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D40"/>
+  <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -11464,7 +11470,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>STM32F042G6</t>
+          <t>STM32F072VB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -11486,7 +11492,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>STM32F042G6</t>
+          <t>STM32F072VB</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -11508,7 +11514,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>STM32F072VB</t>
+          <t>STM32F072RB</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -11530,7 +11536,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>STM32F072VB</t>
+          <t>STM32F072RB</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -11552,12 +11558,12 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>STM32F072RB</t>
+          <t>STM32F042G4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -11567,19 +11573,19 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>STM32F072RB</t>
+          <t>STM32F042K6</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -11589,14 +11595,14 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>STM32F042G4</t>
+          <t>STM32F042K4</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -11611,14 +11617,14 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists UQFPN28 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>STM32F042G4</t>
+          <t>STM32F072R8</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -11640,7 +11646,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>STM32F042G4</t>
+          <t>STM32F072R8</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -11662,12 +11668,12 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>STM32F042K6</t>
+          <t>STM32F072C8</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -11677,19 +11683,19 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>STM32F042K6</t>
+          <t>STM32F072C8</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -11706,12 +11712,12 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>STM32F042K6</t>
+          <t>STM32F042F6</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -11721,19 +11727,19 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>STM32F042K4</t>
+          <t>STM32F072CB</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>Package</t>
+          <t>Timers (16-bit) typ</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -11743,19 +11749,19 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP32, UQFPN32 for this family; the table gives no key to tie a package to this part</t>
+          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>STM32F042K4</t>
+          <t>STM32F072CB</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Timers (32-bit) typ</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -11772,12 +11778,12 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>STM32F042K4</t>
+          <t>STM32F042F4</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -11787,14 +11793,14 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>STM32F072R8</t>
+          <t>STM32F072V8</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -11816,7 +11822,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>STM32F072R8</t>
+          <t>STM32F072V8</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -11838,12 +11844,12 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>STM32F072C8</t>
+          <t>STM32F042C6</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>Timers (16-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -11853,19 +11859,19 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>STM32F072C8</t>
+          <t>STM32F042C4</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Timers (32-bit) typ</t>
+          <t>Package</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -11875,14 +11881,14 @@
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
+          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
         </is>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>STM32F042F6</t>
+          <t>STM32F042T6</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -11897,403 +11903,7 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>STM32F042F6</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="24">
-      <c r="A24" t="inlineStr">
-        <is>
-          <t>STM32F042F6</t>
-        </is>
-      </c>
-      <c r="B24" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C24" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D24" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="25">
-      <c r="A25" t="inlineStr">
-        <is>
-          <t>STM32F072CB</t>
-        </is>
-      </c>
-      <c r="B25" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C25" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D25" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="26">
-      <c r="A26" t="inlineStr">
-        <is>
-          <t>STM32F072CB</t>
-        </is>
-      </c>
-      <c r="B26" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C26" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D26" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="27">
-      <c r="A27" t="inlineStr">
-        <is>
-          <t>STM32F042F4</t>
-        </is>
-      </c>
-      <c r="B27" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C27" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D27" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists TSSOP20 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="28">
-      <c r="A28" t="inlineStr">
-        <is>
-          <t>STM32F042F4</t>
-        </is>
-      </c>
-      <c r="B28" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C28" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D28" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="29">
-      <c r="A29" t="inlineStr">
-        <is>
-          <t>STM32F042F4</t>
-        </is>
-      </c>
-      <c r="B29" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C29" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D29" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="30">
-      <c r="A30" t="inlineStr">
-        <is>
-          <t>STM32F072V8</t>
-        </is>
-      </c>
-      <c r="B30" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C30" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D30" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="31">
-      <c r="A31" t="inlineStr">
-        <is>
-          <t>STM32F072V8</t>
-        </is>
-      </c>
-      <c r="B31" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C31" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D31" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="32">
-      <c r="A32" t="inlineStr">
-        <is>
-          <t>STM32F042C6</t>
-        </is>
-      </c>
-      <c r="B32" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C32" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D32" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="33">
-      <c r="A33" t="inlineStr">
-        <is>
-          <t>STM32F042C6</t>
-        </is>
-      </c>
-      <c r="B33" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C33" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D33" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="34">
-      <c r="A34" t="inlineStr">
-        <is>
-          <t>STM32F042C6</t>
-        </is>
-      </c>
-      <c r="B34" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C34" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D34" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="35">
-      <c r="A35" t="inlineStr">
-        <is>
-          <t>STM32F042C4</t>
-        </is>
-      </c>
-      <c r="B35" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C35" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D35" t="inlineStr">
-        <is>
-          <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists LQFP48, UFQFPN48 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="36">
-      <c r="A36" t="inlineStr">
-        <is>
-          <t>STM32F042C4</t>
-        </is>
-      </c>
-      <c r="B36" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C36" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D36" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="37">
-      <c r="A37" t="inlineStr">
-        <is>
-          <t>STM32F042C4</t>
-        </is>
-      </c>
-      <c r="B37" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C37" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D37" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="38">
-      <c r="A38" t="inlineStr">
-        <is>
-          <t>STM32F042T6</t>
-        </is>
-      </c>
-      <c r="B38" t="inlineStr">
-        <is>
-          <t>Package</t>
-        </is>
-      </c>
-      <c r="C38" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D38" t="inlineStr">
-        <is>
           <t>Table 2. STM32F042x4/x6 device features and peripheral counts lists WLCSP36 for this family; the table gives no key to tie a package to this part</t>
-        </is>
-      </c>
-    </row>
-    <row r="39">
-      <c r="A39" t="inlineStr">
-        <is>
-          <t>STM32F042T6</t>
-        </is>
-      </c>
-      <c r="B39" t="inlineStr">
-        <is>
-          <t>Timers (16-bit) typ</t>
-        </is>
-      </c>
-      <c r="C39" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D39" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
-        </is>
-      </c>
-    </row>
-    <row r="40">
-      <c r="A40" t="inlineStr">
-        <is>
-          <t>STM32F042T6</t>
-        </is>
-      </c>
-      <c r="B40" t="inlineStr">
-        <is>
-          <t>Timers (32-bit) typ</t>
-        </is>
-      </c>
-      <c r="C40" t="inlineStr">
-        <is>
-          <t>AMBIGUOUS</t>
-        </is>
-      </c>
-      <c r="D40" t="inlineStr">
-        <is>
-          <t>Table 7. Timer feature comparison lists the family's timers, but the summary table gives no per-class counts for this variant to join against</t>
         </is>
       </c>
     </row>

--- a/product_selector_out/STM32F0x2.xlsx
+++ b/product_selector_out/STM32F0x2.xlsx
@@ -506,7 +506,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM26"/>
+  <dimension ref="A1:BN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12.4375" customWidth="1" min="1" max="1"/>
@@ -573,7 +573,8 @@
     <col width="21.765625" customWidth="1" min="62" max="62"/>
     <col width="18" customWidth="1" min="63" max="63"/>
     <col width="18" customWidth="1" min="64" max="64"/>
-    <col width="52" customWidth="1" min="65" max="65"/>
+    <col width="18" customWidth="1" min="65" max="65"/>
+    <col width="52" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1"/>
@@ -901,6 +902,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -996,6 +1002,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="3" t="inlineStr">
@@ -1320,6 +1327,11 @@
       </c>
       <c r="BM12" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN12" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -1647,6 +1659,11 @@
       </c>
       <c r="BM13" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN13" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -1974,6 +1991,11 @@
       </c>
       <c r="BM14" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN14" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -2301,6 +2323,11 @@
       </c>
       <c r="BM15" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN15" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -2628,6 +2655,11 @@
       </c>
       <c r="BM16" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN16" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -2955,6 +2987,11 @@
       </c>
       <c r="BM17" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN17" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -3282,6 +3319,11 @@
       </c>
       <c r="BM18" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN18" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -3609,6 +3651,11 @@
       </c>
       <c r="BM19" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN19" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -3936,6 +3983,11 @@
       </c>
       <c r="BM20" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN20" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -4263,6 +4315,11 @@
       </c>
       <c r="BM21" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN21" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -4590,6 +4647,11 @@
       </c>
       <c r="BM22" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN22" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -4917,6 +4979,11 @@
       </c>
       <c r="BM23" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN23" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f072c8.pdf</t>
         </is>
       </c>
@@ -5244,6 +5311,11 @@
       </c>
       <c r="BM24" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN24" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -5571,6 +5643,11 @@
       </c>
       <c r="BM25" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN25" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
@@ -5898,12 +5975,17 @@
       </c>
       <c r="BM26" s="4" t="inlineStr">
         <is>
+          <t>-</t>
+        </is>
+      </c>
+      <c r="BN26" s="4" t="inlineStr">
+        <is>
           <t>https://www.st.com/resource/en/datasheet/stm32f042c4.pdf</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="64">
+  <mergeCells count="65">
     <mergeCell ref="P10:P11"/>
     <mergeCell ref="AS10:AS11"/>
     <mergeCell ref="AD10:AD11"/>
@@ -5924,16 +6006,14 @@
     <mergeCell ref="BA10:BA11"/>
     <mergeCell ref="BG10:BG11"/>
     <mergeCell ref="Q10:Q11"/>
-    <mergeCell ref="A1:BM8"/>
     <mergeCell ref="AR10:AR11"/>
+    <mergeCell ref="AT10:AT11"/>
     <mergeCell ref="S10:S11"/>
-    <mergeCell ref="AT10:AT11"/>
+    <mergeCell ref="BI10:BI11"/>
     <mergeCell ref="AV10:AV11"/>
-    <mergeCell ref="A9:BM9"/>
     <mergeCell ref="BB10:BB11"/>
-    <mergeCell ref="BI10:BI11"/>
+    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="BD10:BD11"/>
-    <mergeCell ref="BM10:BM11"/>
     <mergeCell ref="Y10:Z10"/>
     <mergeCell ref="AC10:AC11"/>
     <mergeCell ref="B10:B11"/>
@@ -5946,6 +6026,7 @@
     <mergeCell ref="AQ10:AQ11"/>
     <mergeCell ref="AW10:AW11"/>
     <mergeCell ref="BH10:BH11"/>
+    <mergeCell ref="BN10:BN11"/>
     <mergeCell ref="AY10:AY11"/>
     <mergeCell ref="BK10:BK11"/>
     <mergeCell ref="A10:A11"/>
@@ -5965,7 +6046,9 @@
     <mergeCell ref="U10:V10"/>
     <mergeCell ref="AG10:AG11"/>
     <mergeCell ref="F10:F11"/>
+    <mergeCell ref="A9:BN9"/>
     <mergeCell ref="H10:H11"/>
+    <mergeCell ref="A1:BN8"/>
     <mergeCell ref="T10:T11"/>
     <mergeCell ref="J10:J11"/>
   </mergeCells>
@@ -5997,7 +6080,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:BM26"/>
+  <dimension ref="A1:BN26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="16" customWidth="1" min="1" max="1"/>
@@ -6065,6 +6148,7 @@
     <col width="16" customWidth="1" min="63" max="63"/>
     <col width="16" customWidth="1" min="64" max="64"/>
     <col width="16" customWidth="1" min="65" max="65"/>
+    <col width="16" customWidth="1" min="66" max="66"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -6398,6 +6482,11 @@
         </is>
       </c>
       <c r="BM10" s="2" t="inlineStr">
+        <is>
+          <t>LPUART typ</t>
+        </is>
+      </c>
+      <c r="BN10" s="2" t="inlineStr">
         <is>
           <t>Datasheet URL</t>
         </is>
@@ -6493,6 +6582,7 @@
       <c r="BK11" s="2" t="n"/>
       <c r="BL11" s="2" t="n"/>
       <c r="BM11" s="2" t="n"/>
+      <c r="BN11" s="2" t="n"/>
     </row>
     <row r="12">
       <c r="A12" s="6" t="inlineStr">
@@ -6815,7 +6905,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM12" s="6" t="inlineStr">
+      <c r="BM12" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN12" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7142,7 +7237,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM13" s="6" t="inlineStr">
+      <c r="BM13" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN13" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7469,7 +7569,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM14" s="6" t="inlineStr">
+      <c r="BM14" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN14" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -7796,7 +7901,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM15" s="6" t="inlineStr">
+      <c r="BM15" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN15" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8123,7 +8233,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM16" s="6" t="inlineStr">
+      <c r="BM16" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN16" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8450,7 +8565,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM17" s="6" t="inlineStr">
+      <c r="BM17" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN17" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -8777,7 +8897,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM18" s="6" t="inlineStr">
+      <c r="BM18" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN18" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9104,7 +9229,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM19" s="6" t="inlineStr">
+      <c r="BM19" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN19" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9431,7 +9561,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM20" s="6" t="inlineStr">
+      <c r="BM20" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN20" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -9758,7 +9893,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM21" s="6" t="inlineStr">
+      <c r="BM21" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN21" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10085,7 +10225,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM22" s="6" t="inlineStr">
+      <c r="BM22" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN22" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10412,7 +10557,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM23" s="6" t="inlineStr">
+      <c r="BM23" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN23" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -10739,7 +10889,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM24" s="6" t="inlineStr">
+      <c r="BM24" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN24" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11066,7 +11221,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM25" s="6" t="inlineStr">
+      <c r="BM25" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN25" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11393,7 +11553,12 @@
           <t>API</t>
         </is>
       </c>
-      <c r="BM26" s="6" t="inlineStr">
+      <c r="BM26" s="9" t="inlineStr">
+        <is>
+          <t>UNAVAILABLE</t>
+        </is>
+      </c>
+      <c r="BN26" s="6" t="inlineStr">
         <is>
           <t>API</t>
         </is>
@@ -11401,8 +11566,8 @@
     </row>
   </sheetData>
   <mergeCells count="2">
-    <mergeCell ref="A9:BM9"/>
-    <mergeCell ref="A1:BM8"/>
+    <mergeCell ref="A9:BN9"/>
+    <mergeCell ref="A1:BN8"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
